--- a/分支1/report/策略检查清单.xlsx
+++ b/分支1/report/策略检查清单.xlsx
@@ -26,15 +26,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="微软雅黑"/>
       <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDCFE7"/>
+        <bgColor rgb="FFBDCFE7"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -51,7 +60,9 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
